--- a/source-data/Enerium_Сет_бонусы_героев_ФИНАЛ.xlsx
+++ b/source-data/Enerium_Сет_бонусы_героев_ФИНАЛ.xlsx
@@ -188,7 +188,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">be3dfa6a580c2254 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">a6044d63401b807e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">физ ДД ловкости</t>
+          <t xml:space="preserve">физ ДД силы</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Огонь</t>
+          <t xml:space="preserve">без стихии</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">контроль (на дебаффы)</t>
+          <t xml:space="preserve">контроль (на контроль)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">

--- a/source-data/Enerium_Сет_бонусы_героев_ФИНАЛ.xlsx
+++ b/source-data/Enerium_Сет_бонусы_героев_ФИНАЛ.xlsx
@@ -188,7 +188,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6044d63401b807e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">82f4117ff5db28a4 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -304,8 +304,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
